--- a/Result/profitability/3332.xlsx
+++ b/Result/profitability/3332.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0.84375</v>
+        <v>0.9387500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>35.6325</v>
+        <v>36.20875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.54</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9875</v>
+        <v>1.07625</v>
       </c>
       <c r="N3" t="n">
-        <v>36.58875</v>
+        <v>36.4825</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.49</v>
       </c>
       <c r="M4" t="n">
-        <v>1.11875</v>
+        <v>1.13875</v>
       </c>
       <c r="N4" t="n">
-        <v>36.63375</v>
+        <v>36.4775</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.02</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1225</v>
+        <v>1.12625</v>
       </c>
       <c r="N5" t="n">
-        <v>36.39875</v>
+        <v>35.64624999999999</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.72</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0725</v>
+        <v>1.11625</v>
       </c>
       <c r="N6" t="n">
-        <v>35.5925</v>
+        <v>35.66375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.35</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01625</v>
+        <v>1.0825</v>
       </c>
       <c r="N7" t="n">
-        <v>35.73</v>
+        <v>35.8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.46</v>
       </c>
       <c r="M8" t="n">
-        <v>0.99625</v>
+        <v>0.9675</v>
       </c>
       <c r="N8" t="n">
-        <v>35.05625</v>
+        <v>34.92125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>1.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0.86875</v>
+        <v>0.8687499999999999</v>
       </c>
       <c r="N11" t="n">
         <v>34.97375</v>
@@ -1899,7 +1899,7 @@
         <v>1.52</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.8724999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>35.6825</v>
@@ -2026,7 +2026,7 @@
         <v>1.17</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8912500000000001</v>
+        <v>0.89125</v>
       </c>
       <c r="N13" t="n">
         <v>36.53625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3332</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>477</v>
+      </c>
+      <c r="D75" t="n">
+        <v>311</v>
+      </c>
+      <c r="E75" t="n">
+        <v>166</v>
+      </c>
+      <c r="F75" t="n">
+        <v>34.82</v>
+      </c>
+      <c r="G75" t="n">
+        <v>45</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.51%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>25</v>
+      </c>
+      <c r="J75" t="n">
+        <v>70</v>
+      </c>
+      <c r="K75" t="n">
+        <v>55</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.8612500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>35.2525</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.079999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03008356545961</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.0299999999999998</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.02678571428571419</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-6.020000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1474045053868757</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
